--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Downtown_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Downtown_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,6 +590,90 @@
         <v>35.74</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TN374</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Natalie's - Lemonade</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TN454</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Mango</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TN362</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Pineapple</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TN380</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Natalie's - Strawberry Lemonade</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
